--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488244_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488244_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. LLANO ABASCAL</t>
+          <t>A. DOBLADO GARCIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0198</v>
+        <v>2.3852</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2152</v>
+        <v>0.8869</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2351</v>
+        <v>1.4982</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.0948</v>
+        <v>3.966</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.0566</v>
+        <v>4.3639</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0382</v>
+        <v>-0.3979</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.7912</v>
+        <v>2.5059</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.9986</v>
+        <v>3.7488</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2074</v>
+        <v>-1.2429</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3035</v>
+        <v>1.4602</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.058</v>
+        <v>0.6152</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2456</v>
+        <v>0.845</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7411</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="R2" t="n">
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4222</v>
+        <v>0.1147</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7994</v>
+        <v>0.1048</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6227</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9513</v>
+        <v>-1.5103</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8883</v>
+        <v>0.3144</v>
       </c>
       <c r="X2" t="n">
-        <v>0.063</v>
+        <v>-1.8247</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DOBLADO GARCIA</t>
+          <t>A. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0923</v>
+        <v>0.8863</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0373</v>
+        <v>-1.3242</v>
       </c>
       <c r="F3" t="n">
-        <v>1.055</v>
+        <v>2.2105</v>
       </c>
       <c r="G3" t="n">
-        <v>3.966</v>
+        <v>-3.0948</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3639</v>
+        <v>-3.0566</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3979</v>
+        <v>-0.0382</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5059</v>
+        <v>-2.7912</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7488</v>
+        <v>-2.9986</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.2429</v>
+        <v>0.2074</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4602</v>
+        <v>-0.3035</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6152</v>
+        <v>-0.058</v>
       </c>
       <c r="O3" t="n">
-        <v>0.845</v>
+        <v>-0.2456</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1853</v>
+        <v>0.7411</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="R3" t="n">
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1781</v>
+        <v>1.2886</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7449</v>
+        <v>0.6905</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4333</v>
+        <v>0.5981</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.5103</v>
+        <v>1.9513</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3144</v>
+        <v>1.8883</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.8247</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1065</v>
+        <v>0.5901</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4536</v>
+        <v>1.7497</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3471</v>
+        <v>-1.1597</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3142</v>
@@ -766,13 +766,13 @@
         <v>2.594</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1522</v>
+        <v>0.6358</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.5992</v>
+        <v>-0.3031</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7513</v>
+        <v>0.9388</v>
       </c>
       <c r="V4" t="n">
         <v>-2.1403</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0197</v>
+        <v>-0.0968</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8924</v>
+        <v>-1.0335</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9121</v>
+        <v>0.9368</v>
       </c>
       <c r="G5" t="n">
         <v>-1.5066</v>
@@ -844,13 +844,13 @@
         <v>1.297</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2783</v>
+        <v>-0.3948</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0721</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3504</v>
+        <v>-0.3258</v>
       </c>
       <c r="V5" t="n">
         <v>0.6929999999999999</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. NAVARRO GARRIDO</t>
+          <t>A. DIAZ MACIAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7105</v>
+        <v>-0.8657</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-3.5566</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1839</v>
+        <v>2.6909</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.979</v>
+        <v>-1.3717</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.95</v>
+        <v>0.3516</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.029</v>
+        <v>-1.7233</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5669999999999999</v>
+        <v>0.5401</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.1706</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.412</v>
+        <v>-0.7412</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.383</v>
+        <v>-0.1885</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.029</v>
+        <v>-0.5527</v>
       </c>
       <c r="P6" t="n">
-        <v>1.297</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.8175</v>
       </c>
       <c r="R6" t="n">
-        <v>1.297</v>
+        <v>2.7793</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6014</v>
+        <v>0.9709</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6703</v>
+        <v>0.3181</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0689</v>
+        <v>0.6528</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.63</v>
+        <v>1.5733</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.63</v>
+        <v>1.5733</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DIAZ MACIAS</t>
+          <t>S. NAVARRO GARRIDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3548</v>
+        <v>-1.1695</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.8734</v>
+        <v>-1.0595</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5185</v>
+        <v>-0.11</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3717</v>
+        <v>-1.979</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3516</v>
+        <v>-0.95</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7233</v>
+        <v>-1.029</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5401</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1706</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7412</v>
+        <v>-1.412</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1885</v>
+        <v>-0.383</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5527</v>
+        <v>-1.029</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0382</v>
+        <v>1.297</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.8175</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7793</v>
+        <v>1.297</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4818</v>
+        <v>0.1424</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0013</v>
+        <v>0.1374</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4805</v>
+        <v>0.005</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5733</v>
+        <v>-0.63</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5733</v>
+        <v>-0.63</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7537</v>
+        <v>-1.2815</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2486</v>
+        <v>-0.998</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5051</v>
+        <v>-0.2835</v>
       </c>
       <c r="G8" t="n">
         <v>0.6783</v>
@@ -1078,13 +1078,13 @@
         <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.2643</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4924</v>
+        <v>-0.2419</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.244</v>
+        <v>-0.0224</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5103</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.814</v>
+        <v>-1.9371</v>
       </c>
       <c r="E9" t="n">
         <v>-1.8689</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0549</v>
+        <v>-0.0682</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7843</v>
@@ -1156,13 +1156,13 @@
         <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1032</v>
+        <v>-0.2263</v>
       </c>
       <c r="T9" t="n">
         <v>-0.3071</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2039</v>
+        <v>0.0808</v>
       </c>
       <c r="V9" t="n">
         <v>1.2589</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4138</v>
+        <v>-2.2359</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3427</v>
+        <v>-0.288</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.071</v>
+        <v>-1.9479</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8567</v>
@@ -1234,13 +1234,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5745</v>
+        <v>-0.3967</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.526</v>
+        <v>-0.4713</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0485</v>
+        <v>0.0746</v>
       </c>
       <c r="V10" t="n">
         <v>0.3144</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6276</v>
+        <v>-2.6167</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7169</v>
+        <v>-2.6074</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0893</v>
+        <v>-0.0092</v>
       </c>
       <c r="G11" t="n">
         <v>-2.96</v>
@@ -1312,13 +1312,13 @@
         <v>2.0382</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1095</v>
+        <v>1.1204</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1443</v>
+        <v>0.2537</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.8667</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8888</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.436100000000001</v>
+        <v>-6.3416</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.1939</v>
+        <v>-10.0995</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7578</v>
+        <v>3.7579</v>
       </c>
       <c r="G12" t="n">
         <v>-10.223</v>
@@ -1390,10 +1390,10 @@
         <v>15.7494</v>
       </c>
       <c r="S12" t="n">
-        <v>1.896600000000001</v>
+        <v>2.9907</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9822000000000001</v>
+        <v>0.1121000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>2.8785</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5524</v>
+        <v>5.4304</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1326</v>
+        <v>4.9367</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4198</v>
+        <v>0.4937</v>
       </c>
       <c r="G13" t="n">
         <v>4.824</v>
@@ -1468,13 +1468,13 @@
         <v>0.7411</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3017</v>
+        <v>0.1797</v>
       </c>
       <c r="T13" t="n">
-        <v>0.051</v>
+        <v>-0.1449</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2507</v>
+        <v>0.3245</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3144</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.147</v>
+        <v>4.915</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3156</v>
+        <v>2.8052</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8315</v>
+        <v>2.1098</v>
       </c>
       <c r="G14" t="n">
         <v>2.0489</v>
@@ -1546,13 +1546,13 @@
         <v>0.9264</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4027</v>
+        <v>0.3653</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4377</v>
+        <v>0.0519</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0351</v>
+        <v>0.3134</v>
       </c>
       <c r="V14" t="n">
         <v>1.5744</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4997</v>
+        <v>3.7663</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7382</v>
+        <v>0.8015</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7615</v>
+        <v>2.9648</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8297</v>
+        <v>2.641</v>
       </c>
       <c r="H15" t="n">
-        <v>2.269</v>
+        <v>0.119</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5607</v>
+        <v>2.522</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0661</v>
+        <v>2.1758</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1122</v>
+        <v>-0.4381</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9538</v>
+        <v>2.6139</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.4652</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1567</v>
+        <v>0.5572</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6069</v>
+        <v>-0.092</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R15" t="n">
-        <v>1.297</v>
+        <v>2.4087</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7817</v>
+        <v>-0.3749</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1926</v>
+        <v>-0.7803</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5891999999999999</v>
+        <v>0.4054</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6294</v>
+        <v>0.9444</v>
       </c>
       <c r="W15" t="n">
         <v>1.2589</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8883</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9669</v>
+        <v>2.6264</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2139</v>
+        <v>1.7589</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7529</v>
+        <v>0.8675</v>
       </c>
       <c r="G16" t="n">
-        <v>2.641</v>
+        <v>3.8297</v>
       </c>
       <c r="H16" t="n">
-        <v>0.119</v>
+        <v>2.269</v>
       </c>
       <c r="I16" t="n">
-        <v>2.522</v>
+        <v>1.5607</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1758</v>
+        <v>3.0661</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4381</v>
+        <v>2.1122</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6139</v>
+        <v>0.9538</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4652</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5572</v>
+        <v>0.1567</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.092</v>
+        <v>0.6069</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4087</v>
+        <v>1.297</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1744</v>
+        <v>0.9084</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3679</v>
+        <v>0.2133</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1935</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9444</v>
+        <v>-0.6294</v>
       </c>
       <c r="W16" t="n">
         <v>1.2589</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3144</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6208</v>
+        <v>1.2238</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0398</v>
+        <v>-1.5502</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6606</v>
+        <v>2.774</v>
       </c>
       <c r="G17" t="n">
         <v>0.1431</v>
@@ -1780,13 +1780,13 @@
         <v>2.2234</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1518</v>
+        <v>-0.5487</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4226</v>
+        <v>-0.9329</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2708</v>
+        <v>0.3842</v>
       </c>
       <c r="V17" t="n">
         <v>1.2589</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LOPEZ</t>
+          <t>T. LUCERO BARBEITO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4215</v>
+        <v>-0.1416</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2475</v>
+        <v>-0.5147</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.669</v>
+        <v>0.3731</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0958</v>
+        <v>0.3745</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3111</v>
+        <v>-0.6192</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7847</v>
+        <v>0.9937</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3878</v>
+        <v>0.5336</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3865</v>
+        <v>-0.2449</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0013</v>
+        <v>0.7785</v>
       </c>
       <c r="M18" t="n">
-        <v>0.708</v>
+        <v>-0.1591</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.3743</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7834</v>
+        <v>0.2152</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.594</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0211</v>
+        <v>0.1694</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3246</v>
+        <v>0.1931</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3034</v>
+        <v>-0.0236</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9444</v>
+        <v>-0.315</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3144</v>
+        <v>-0.315</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. LUCERO BARBEITO</t>
+          <t>A. RODRIGUEZ LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9749</v>
+        <v>-0.3385</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2002</v>
+        <v>-0.0463</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2254</v>
+        <v>-0.2922</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3745</v>
+        <v>3.0958</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6192</v>
+        <v>0.3111</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9937</v>
+        <v>2.7847</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5336</v>
+        <v>2.3878</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2449</v>
+        <v>0.3865</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7785</v>
+        <v>2.0013</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1591</v>
+        <v>0.708</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3743</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2152</v>
+        <v>0.7834</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3706</v>
+        <v>-2.594</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6637999999999999</v>
+        <v>0.1041</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4924</v>
+        <v>0.0308</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1714</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.315</v>
+        <v>-0.9444</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.315</v>
+        <v>0.3144</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7867</v>
+        <v>-2.0067</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8704</v>
+        <v>-2.5559</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0837</v>
+        <v>0.5493</v>
       </c>
       <c r="G20" t="n">
         <v>-1.213</v>
@@ -2014,13 +2014,13 @@
         <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0179</v>
+        <v>-0.2378</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4303</v>
+        <v>-0.2552</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4482</v>
+        <v>0.0174</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8263</v>
+        <v>-2.9832</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9619</v>
+        <v>-3.0599</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1356</v>
+        <v>0.0767</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7127</v>
@@ -2092,13 +2092,13 @@
         <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.058</v>
+        <v>-0.2148</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2226</v>
+        <v>-0.3205</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1646</v>
+        <v>0.1057</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3144</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3414</v>
+        <v>-3.0974</v>
       </c>
       <c r="E22" t="n">
         <v>-6.3331</v>
       </c>
       <c r="F22" t="n">
-        <v>2.9917</v>
+        <v>3.2357</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8084</v>
@@ -2170,13 +2170,13 @@
         <v>2.2234</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5325</v>
+        <v>-0.2885</v>
       </c>
       <c r="T22" t="n">
         <v>-0.9339</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4014</v>
+        <v>0.6454</v>
       </c>
       <c r="V22" t="n">
         <v>0.6289</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.436</v>
+        <v>9.394499999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7576</v>
+        <v>-3.757799999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>11.1937</v>
+        <v>13.1524</v>
       </c>
       <c r="G23" t="n">
         <v>10.2229</v>
@@ -2233,7 +2233,7 @@
         <v>1.6452</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2616</v>
+        <v>0.2615999999999999</v>
       </c>
       <c r="O23" t="n">
         <v>1.3837</v>
@@ -2248,13 +2248,13 @@
         <v>12.9699</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8966</v>
+        <v>0.06220000000000003</v>
       </c>
       <c r="T23" t="n">
         <v>-2.8786</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9823000000000001</v>
+        <v>2.9409</v>
       </c>
       <c r="V23" t="n">
         <v>1.889</v>
